--- a/data/trans_orig/P79A7_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P79A7_2023-Habitat-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,27 +1068,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>899</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>7596</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3693</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>9173</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4480</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>59,74%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>9173</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>9173</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>9173</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,27 +1411,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>967</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1481,27 +1481,27 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>967</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1604,12 +1604,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>80,67%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>695</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>695</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>695</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>695</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9047</t>
+          <t>10147</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2167,27 +2167,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>15721</t>
+          <t>17477</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10286</t>
+          <t>11459</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>20556</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>7263</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8760</t>
+          <t>9097</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>44,25%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>20556</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>20556</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>20556</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
